--- a/data/PaymentPrediction-Demo.xlsx
+++ b/data/PaymentPrediction-Demo.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="L2" s="11" t="n">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>20</v>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="L3" s="11" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>4</v>
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="L4" s="11" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>-8</v>
@@ -5764,10 +5764,10 @@
         </is>
       </c>
       <c r="L5" s="11" t="n">
-        <v>46214</v>
+        <v>46218</v>
       </c>
       <c r="M5" s="11" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>-18</v>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="L6" s="11" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>-15</v>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="L7" s="11" t="n">
-        <v>46215</v>
+        <v>46219</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>-19</v>
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="L8" s="11" t="n">
-        <v>46225</v>
+        <v>46229</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>-29</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="L9" s="11" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>-15</v>
@@ -6124,10 +6124,10 @@
         </is>
       </c>
       <c r="L10" s="11" t="n">
-        <v>46215</v>
+        <v>46219</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>-19</v>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="L11" s="11" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>-31</v>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="L12" s="11" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>4</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="L13" s="11" t="n">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>-6</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="L14" s="11" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>-20</v>
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="L15" s="11" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>3</v>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="L16" s="11" t="n">
-        <v>46203</v>
+        <v>46207</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>-7</v>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="L17" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>-17</v>
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="L18" s="11" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>68</v>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="L19" s="11" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>46186</v>
+        <v>46190</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>40</v>
@@ -6856,10 +6856,10 @@
         </is>
       </c>
       <c r="L20" s="11" t="n">
-        <v>46180</v>
+        <v>46184</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>46210</v>
+        <v>46214</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>16</v>
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="L21" s="11" t="n">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>66</v>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="L22" s="11" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>38</v>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="L23" s="11" t="n">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>13</v>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="L24" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>-17</v>
@@ -7224,10 +7224,10 @@
         </is>
       </c>
       <c r="L25" s="11" t="n">
-        <v>46214</v>
+        <v>46218</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>-18</v>
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="L26" s="11" t="n">
-        <v>46224</v>
+        <v>46228</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>-28</v>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="L27" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>-17</v>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="L28" s="11" t="n">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>-26</v>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="L29" s="11" t="n">
-        <v>46190</v>
+        <v>46194</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>6</v>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="L30" s="11" t="n">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>-10</v>
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="L31" s="11" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>-20</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="L32" s="11" t="n">
-        <v>46190</v>
+        <v>46194</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="N32" s="2" t="n">
         <v>6</v>
@@ -7804,10 +7804,10 @@
         </is>
       </c>
       <c r="L33" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>-12</v>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="L34" s="11" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>-15</v>
@@ -7952,10 +7952,10 @@
         </is>
       </c>
       <c r="L35" s="11" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>46221</v>
+        <v>46225</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>5</v>
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="L36" s="11" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="N36" s="2" t="n">
         <v>-8</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="L37" s="11" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>-16</v>
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="L38" s="11" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>38</v>
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="L39" s="11" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>46210</v>
+        <v>46214</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>16</v>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="L40" s="11" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>64</v>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="L41" s="11" t="n">
-        <v>46159</v>
+        <v>46163</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>37</v>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="L42" s="11" t="n">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="N42" s="2" t="n">
         <v>13</v>
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="L43" s="11" t="n">
-        <v>45998</v>
+        <v>46002</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>46028</v>
+        <v>46032</v>
       </c>
       <c r="N43" s="2" t="n">
         <v>198</v>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="L44" s="11" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>162</v>
@@ -8704,10 +8704,10 @@
         </is>
       </c>
       <c r="L45" s="11" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>46110</v>
+        <v>46114</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>116</v>
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="L46" s="11" t="n">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>46147</v>
+        <v>46151</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>79</v>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="L47" s="11" t="n">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="N47" s="2" t="n">
         <v>45</v>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="L48" s="11" t="n">
-        <v>46210</v>
+        <v>46214</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>-14</v>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="L49" s="11" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="N49" s="2" t="n">
         <v>-24</v>
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="L50" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>-27</v>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="L51" s="11" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>46221</v>
+        <v>46225</v>
       </c>
       <c r="N51" s="2" t="n">
         <v>5</v>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="L52" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="N52" s="2" t="n">
         <v>-12</v>
@@ -9288,10 +9288,10 @@
         </is>
       </c>
       <c r="L53" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>3</v>
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="L54" s="11" t="n">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>-11</v>
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="L55" s="11" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="N55" s="2" t="n">
         <v>-21</v>
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="L56" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="N56" s="2" t="n">
         <v>3</v>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="L57" s="11" t="n">
-        <v>46217</v>
+        <v>46221</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="N57" s="2" t="n">
         <v>-6</v>
@@ -9648,10 +9648,10 @@
         </is>
       </c>
       <c r="L58" s="11" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="N58" s="2" t="n">
         <v>-16</v>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="L59" s="11" t="n">
-        <v>46225</v>
+        <v>46229</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="N59" s="2" t="n">
         <v>-14</v>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="L60" s="11" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="N60" s="2" t="n">
         <v>-27</v>
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="L61" s="11" t="n">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>46217</v>
+        <v>46221</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>9</v>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="L62" s="11" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="N62" s="2" t="n">
         <v>-11</v>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="L63" s="11" t="n">
-        <v>46196</v>
+        <v>46200</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>-15</v>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="L64" s="11" t="n">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="N64" s="2" t="n">
         <v>64</v>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="L65" s="11" t="n">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="N65" s="2" t="n">
         <v>37</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="L66" s="11" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="N66" s="2" t="n">
         <v>18</v>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="L67" s="11" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="N67" s="2" t="n">
         <v>3</v>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="L68" s="11" t="n">
-        <v>46187</v>
+        <v>46191</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="N68" s="2" t="n">
         <v>-6</v>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="L69" s="11" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="N69" s="2" t="n">
         <v>4</v>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="L70" s="11" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="N70" s="2" t="n">
         <v>-11</v>
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="L71" s="11" t="n">
-        <v>46001</v>
+        <v>46005</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="N71" s="2" t="n">
         <v>195</v>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="L72" s="11" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="N72" s="2" t="n">
         <v>162</v>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="L73" s="11" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>46110</v>
+        <v>46114</v>
       </c>
       <c r="N73" s="2" t="n">
         <v>116</v>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="L74" s="11" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="N74" s="2" t="n">
         <v>75</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="L75" s="11" t="n">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="N75" s="2" t="n">
         <v>48</v>
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="L76" s="11" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="N76" s="2" t="n">
         <v>4</v>
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="L77" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="M77" s="11" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="N77" s="2" t="n">
         <v>-12</v>
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="L78" s="11" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="M78" s="11" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="N78" s="2" t="n">
         <v>-16</v>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="L79" s="11" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="M79" s="11" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="N79" s="2" t="n">
         <v>64</v>
@@ -11272,10 +11272,10 @@
         </is>
       </c>
       <c r="L80" s="11" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="M80" s="11" t="n">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="N80" s="2" t="n">
         <v>38</v>
@@ -11348,10 +11348,10 @@
         </is>
       </c>
       <c r="L81" s="11" t="n">
-        <v>46166</v>
+        <v>46170</v>
       </c>
       <c r="M81" s="11" t="n">
-        <v>46196</v>
+        <v>46200</v>
       </c>
       <c r="N81" s="2" t="n">
         <v>30</v>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="L82" s="11" t="n">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="M82" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="N82" s="2" t="n">
         <v>13</v>
@@ -11496,10 +11496,10 @@
         </is>
       </c>
       <c r="L83" s="11" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="M83" s="11" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="N83" s="2" t="n">
         <v>-15</v>
@@ -11568,10 +11568,10 @@
         </is>
       </c>
       <c r="L84" s="11" t="n">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="M84" s="11" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="N84" s="2" t="n">
         <v>-22</v>
@@ -11640,10 +11640,10 @@
         </is>
       </c>
       <c r="L85" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="M85" s="11" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="N85" s="2" t="n">
         <v>-27</v>
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="L86" s="11" t="n">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="M86" s="11" t="n">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="N86" s="2" t="n">
         <v>66</v>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="L87" s="11" t="n">
-        <v>46159</v>
+        <v>46163</v>
       </c>
       <c r="M87" s="11" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="N87" s="2" t="n">
         <v>37</v>
@@ -11868,10 +11868,10 @@
         </is>
       </c>
       <c r="L88" s="11" t="n">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="M88" s="11" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="N88" s="2" t="n">
         <v>13</v>
@@ -11944,10 +11944,10 @@
         </is>
       </c>
       <c r="L89" s="11" t="n">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="M89" s="11" t="n">
-        <v>46161</v>
+        <v>46165</v>
       </c>
       <c r="N89" s="2" t="n">
         <v>65</v>
@@ -12020,10 +12020,10 @@
         </is>
       </c>
       <c r="L90" s="11" t="n">
-        <v>46159</v>
+        <v>46163</v>
       </c>
       <c r="M90" s="11" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="N90" s="2" t="n">
         <v>37</v>
@@ -12092,10 +12092,10 @@
         </is>
       </c>
       <c r="L91" s="11" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="M91" s="11" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="N91" s="2" t="n">
         <v>17</v>
@@ -12164,10 +12164,10 @@
         </is>
       </c>
       <c r="L92" s="11" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="M92" s="11" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="N92" s="2" t="n">
         <v>3</v>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="L93" s="11" t="n">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="M93" s="11" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="N93" s="2" t="n">
         <v>-10</v>
@@ -12308,10 +12308,10 @@
         </is>
       </c>
       <c r="L94" s="11" t="n">
-        <v>46214</v>
+        <v>46218</v>
       </c>
       <c r="M94" s="11" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="N94" s="2" t="n">
         <v>-18</v>
@@ -12384,10 +12384,10 @@
         </is>
       </c>
       <c r="L95" s="11" t="n">
-        <v>45997</v>
+        <v>46001</v>
       </c>
       <c r="M95" s="11" t="n">
-        <v>46027</v>
+        <v>46031</v>
       </c>
       <c r="N95" s="2" t="n">
         <v>199</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="L96" s="11" t="n">
-        <v>46036</v>
+        <v>46040</v>
       </c>
       <c r="M96" s="11" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>160</v>
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="L97" s="11" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="M97" s="11" t="n">
-        <v>46105</v>
+        <v>46109</v>
       </c>
       <c r="N97" s="2" t="n">
         <v>121</v>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="L98" s="11" t="n">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="M98" s="11" t="n">
-        <v>46145</v>
+        <v>46149</v>
       </c>
       <c r="N98" s="2" t="n">
         <v>81</v>
@@ -12688,10 +12688,10 @@
         </is>
       </c>
       <c r="L99" s="11" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="M99" s="11" t="n">
-        <v>46180</v>
+        <v>46184</v>
       </c>
       <c r="N99" s="2" t="n">
         <v>46</v>
@@ -12764,10 +12764,10 @@
         </is>
       </c>
       <c r="L100" s="11" t="n">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="M100" s="11" t="n">
-        <v>46161</v>
+        <v>46165</v>
       </c>
       <c r="N100" s="2" t="n">
         <v>65</v>
@@ -12840,10 +12840,10 @@
         </is>
       </c>
       <c r="L101" s="11" t="n">
-        <v>46159</v>
+        <v>46163</v>
       </c>
       <c r="M101" s="11" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="N101" s="2" t="n">
         <v>37</v>
@@ -12916,10 +12916,10 @@
         </is>
       </c>
       <c r="L102" s="11" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="M102" s="11" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="N102" s="2" t="n">
         <v>17</v>
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="L103" s="11" t="n">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="M103" s="11" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="N103" s="2" t="n">
         <v>196</v>
@@ -13068,10 +13068,10 @@
         </is>
       </c>
       <c r="L104" s="11" t="n">
-        <v>46029</v>
+        <v>46033</v>
       </c>
       <c r="M104" s="11" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="N104" s="2" t="n">
         <v>167</v>
@@ -13144,10 +13144,10 @@
         </is>
       </c>
       <c r="L105" s="11" t="n">
-        <v>46078</v>
+        <v>46082</v>
       </c>
       <c r="M105" s="11" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="N105" s="2" t="n">
         <v>118</v>
@@ -13220,10 +13220,10 @@
         </is>
       </c>
       <c r="L106" s="11" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="M106" s="11" t="n">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="N106" s="2" t="n">
         <v>78</v>
@@ -13296,10 +13296,10 @@
         </is>
       </c>
       <c r="L107" s="11" t="n">
-        <v>46152</v>
+        <v>46156</v>
       </c>
       <c r="M107" s="11" t="n">
-        <v>46182</v>
+        <v>46186</v>
       </c>
       <c r="N107" s="2" t="n">
         <v>44</v>
@@ -13372,10 +13372,10 @@
         </is>
       </c>
       <c r="L108" s="11" t="n">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="M108" s="11" t="n">
-        <v>46029</v>
+        <v>46033</v>
       </c>
       <c r="N108" s="2" t="n">
         <v>197</v>
@@ -13448,10 +13448,10 @@
         </is>
       </c>
       <c r="L109" s="11" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="M109" s="11" t="n">
-        <v>46068</v>
+        <v>46072</v>
       </c>
       <c r="N109" s="2" t="n">
         <v>158</v>
@@ -13524,10 +13524,10 @@
         </is>
       </c>
       <c r="L110" s="11" t="n">
-        <v>46043</v>
+        <v>46047</v>
       </c>
       <c r="M110" s="11" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="N110" s="2" t="n">
         <v>153</v>
@@ -13600,10 +13600,10 @@
         </is>
       </c>
       <c r="L111" s="11" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="M111" s="11" t="n">
-        <v>46106</v>
+        <v>46110</v>
       </c>
       <c r="N111" s="2" t="n">
         <v>120</v>
@@ -13676,10 +13676,10 @@
         </is>
       </c>
       <c r="L112" s="11" t="n">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="M112" s="11" t="n">
-        <v>46147</v>
+        <v>46151</v>
       </c>
       <c r="N112" s="2" t="n">
         <v>79</v>
@@ -13752,10 +13752,10 @@
         </is>
       </c>
       <c r="L113" s="11" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="M113" s="11" t="n">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="N113" s="2" t="n">
         <v>43</v>
@@ -13828,10 +13828,10 @@
         </is>
       </c>
       <c r="L114" s="11" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="M114" s="11" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="N114" s="2" t="n">
         <v>68</v>
@@ -13904,10 +13904,10 @@
         </is>
       </c>
       <c r="L115" s="11" t="n">
-        <v>46161</v>
+        <v>46165</v>
       </c>
       <c r="M115" s="11" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="N115" s="2" t="n">
         <v>35</v>
@@ -13980,10 +13980,10 @@
         </is>
       </c>
       <c r="L116" s="11" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="M116" s="11" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="N116" s="2" t="n">
         <v>18</v>
@@ -14056,10 +14056,10 @@
         </is>
       </c>
       <c r="L117" s="11" t="n">
-        <v>46016</v>
+        <v>46020</v>
       </c>
       <c r="M117" s="11" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="N117" s="2" t="n">
         <v>195</v>
@@ -14132,10 +14132,10 @@
         </is>
       </c>
       <c r="L118" s="11" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="M118" s="11" t="n">
-        <v>46063</v>
+        <v>46067</v>
       </c>
       <c r="N118" s="2" t="n">
         <v>163</v>
@@ -14208,10 +14208,10 @@
         </is>
       </c>
       <c r="L119" s="11" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="M119" s="11" t="n">
-        <v>46110</v>
+        <v>46114</v>
       </c>
       <c r="N119" s="2" t="n">
         <v>116</v>
@@ -14284,10 +14284,10 @@
         </is>
       </c>
       <c r="L120" s="11" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="M120" s="11" t="n">
-        <v>46147</v>
+        <v>46151</v>
       </c>
       <c r="N120" s="2" t="n">
         <v>79</v>
@@ -14360,10 +14360,10 @@
         </is>
       </c>
       <c r="L121" s="11" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
       <c r="M121" s="11" t="n">
-        <v>46180</v>
+        <v>46184</v>
       </c>
       <c r="N121" s="2" t="n">
         <v>46</v>
@@ -14533,7 +14533,7 @@
         <v>11122.93</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="I2" s="8" t="n">
         <v>51059.19</v>
@@ -14590,7 +14590,7 @@
         <v>18250.31</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>46196</v>
+        <v>46200</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>46619.5</v>
@@ -14647,7 +14647,7 @@
         <v>20028.38</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="I4" s="8" t="n">
         <v>41597.49</v>
@@ -14704,7 +14704,7 @@
         <v>26457.45</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>48978.44</v>
@@ -14761,7 +14761,7 @@
         <v>4912.32</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>46180</v>
+        <v>46184</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>23562.1</v>
@@ -14818,7 +14818,7 @@
         <v>8014.32</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>28914.71</v>
@@ -14875,7 +14875,7 @@
         <v>11911.9</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>24871.05</v>
@@ -14932,7 +14932,7 @@
         <v>5371.09</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>28509.49</v>
@@ -14989,7 +14989,7 @@
         <v>20817.13</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>38634.8</v>
@@ -15046,7 +15046,7 @@
         <v>8284.9</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>34027.36</v>
@@ -15103,7 +15103,7 @@
         <v>12934.78</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>34820.27</v>
@@ -15160,7 +15160,7 @@
         <v>6578.22</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="I13" s="8" t="n">
         <v>16454.79</v>
@@ -15217,7 +15217,7 @@
         <v>6478.45</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>11693.1</v>
@@ -15274,7 +15274,7 @@
         <v>4416.78</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>21200.33</v>
@@ -15331,7 +15331,7 @@
         <v>8121.32</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>44792.13</v>
@@ -15388,7 +15388,7 @@
         <v>5070.1</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>46200</v>
+        <v>46204</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>21779.66</v>
@@ -15445,7 +15445,7 @@
         <v>9291.24</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>14492.42</v>
@@ -15502,7 +15502,7 @@
         <v>23741.26</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>43598.63</v>
@@ -15559,7 +15559,7 @@
         <v>7548.5</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>28743</v>
@@ -15616,7 +15616,7 @@
         <v>12047.75</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>46187</v>
+        <v>46191</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>41682.32</v>
@@ -15673,7 +15673,7 @@
         <v>149777.15</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>249145.92</v>
@@ -15730,7 +15730,7 @@
         <v>222271.36</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>46194</v>
+        <v>46198</v>
       </c>
       <c r="I23" s="8" t="n">
         <v>444324.63</v>
@@ -15787,7 +15787,7 @@
         <v>74133.82000000001</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>46196</v>
+        <v>46200</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>242274.34</v>
@@ -15844,7 +15844,7 @@
         <v>170679.76</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>46182</v>
+        <v>46186</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>328257.87</v>
@@ -15901,7 +15901,7 @@
         <v>15125.66</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>39255.67</v>
@@ -15958,7 +15958,7 @@
         <v>81015.91</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>46194</v>
+        <v>46198</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>138902.64</v>
@@ -16015,7 +16015,7 @@
         <v>69914.50999999999</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>200754.33</v>
@@ -16072,7 +16072,7 @@
         <v>46151.16</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>139212.81</v>
@@ -16129,7 +16129,7 @@
         <v>53314.35</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="I30" s="8" t="n">
         <v>114627.76</v>
@@ -16186,7 +16186,7 @@
         <v>5074.44</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>46173</v>
+        <v>46177</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>11588.7</v>
@@ -16243,7 +16243,7 @@
         <v>93500.06</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="I32" s="8" t="n">
         <v>184943.3</v>
@@ -16300,7 +16300,7 @@
         <v>9380.709999999999</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>14441.09</v>
@@ -16357,7 +16357,7 @@
         <v>8200.6</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>46140</v>
+        <v>46144</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>14413.11</v>
@@ -16414,7 +16414,7 @@
         <v>2497.01</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>7694.66</v>
@@ -16471,7 +16471,7 @@
         <v>5836.56</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>46092</v>
+        <v>46096</v>
       </c>
       <c r="I36" s="8" t="n">
         <v>9215.459999999999</v>
@@ -16528,7 +16528,7 @@
         <v>3440.71</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>10789.41</v>
@@ -16585,7 +16585,7 @@
         <v>9628.58</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>46099</v>
+        <v>46103</v>
       </c>
       <c r="I38" s="8" t="n">
         <v>18131.89</v>
@@ -16711,7 +16711,7 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>21923.78</v>
@@ -16749,7 +16749,7 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>46619.5</v>
@@ -16787,7 +16787,7 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>41597.49</v>
@@ -16825,7 +16825,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>31200.42</v>
@@ -16863,7 +16863,7 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>16290.6</v>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>0</v>
@@ -16939,7 +16939,7 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>0</v>
@@ -16977,7 +16977,7 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>28509.49</v>
@@ -17015,7 +17015,7 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>38634.8</v>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E11" s="8" t="n">
         <v>21142.88</v>
@@ -17091,7 +17091,7 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>20698.95</v>
@@ -17129,7 +17129,7 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>12022.69</v>
@@ -17167,7 +17167,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>0</v>
@@ -17205,7 +17205,7 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>0</v>
@@ -17281,7 +17281,7 @@
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>21779.66</v>
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>8858.110000000001</v>
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>33700.72</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>24374.52</v>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>41682.32</v>
@@ -17471,7 +17471,7 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>76815.16</v>
@@ -17509,7 +17509,7 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>11522.77</v>
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>18340.96</v>
@@ -17623,7 +17623,7 @@
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>115298.74</v>
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>0</v>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>139212.81</v>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>0</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>0</v>
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="D32" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>167644.89</v>
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>0</v>
@@ -17927,7 +17927,7 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>0</v>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>0</v>
@@ -18041,7 +18041,7 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E37" s="8" t="n">
         <v>0</v>
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>0</v>

--- a/data/PaymentPrediction-Demo.xlsx
+++ b/data/PaymentPrediction-Demo.xlsx
@@ -32,8 +32,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,7 +118,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4281,10 +4282,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="L2" s="11" t="n">
         <v>46222</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M2" s="11" t="n">
         <v>46252</v>
       </c>
       <c r="N2" s="2" t="n">
@@ -4353,10 +4354,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L3" s="10" t="n">
+      <c r="L3" s="11" t="n">
         <v>46230</v>
       </c>
-      <c r="M3" s="10" t="n">
+      <c r="M3" s="11" t="n">
         <v>46260</v>
       </c>
       <c r="N3" s="2" t="n">
@@ -4425,10 +4426,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="11" t="n">
         <v>46232</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="11" t="n">
         <v>46262</v>
       </c>
       <c r="N4" s="2" t="n">
@@ -4497,10 +4498,10 @@
           <t>Pension benefit calculation &amp; processing</t>
         </is>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="11" t="n">
         <v>46209</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="11" t="n">
         <v>46254</v>
       </c>
       <c r="N5" s="2" t="n">
@@ -4569,10 +4570,10 @@
           <t>Trustee meeting &amp; fund accounting support</t>
         </is>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="L6" s="11" t="n">
         <v>46211</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="11" t="n">
         <v>46256</v>
       </c>
       <c r="N6" s="2" t="n">
@@ -4641,10 +4642,10 @@
           <t>Fund administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="L7" s="11" t="n">
         <v>46218</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="11" t="n">
         <v>46263</v>
       </c>
       <c r="N7" s="2" t="n">
@@ -4713,10 +4714,10 @@
           <t>Pension benefit calculation &amp; processing</t>
         </is>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="11" t="n">
         <v>46221</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="11" t="n">
         <v>46251</v>
       </c>
       <c r="N8" s="2" t="n">
@@ -4785,10 +4786,10 @@
           <t>Trustee meeting &amp; fund accounting support</t>
         </is>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="11" t="n">
         <v>46227</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>46257</v>
       </c>
       <c r="N9" s="2" t="n">
@@ -4857,10 +4858,10 @@
           <t>Fund administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="11" t="n">
         <v>46237</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="N10" s="2" t="n">
@@ -4929,10 +4930,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="11" t="n">
         <v>46198</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="11" t="n">
         <v>46228</v>
       </c>
       <c r="N11" s="2" t="n">
@@ -5001,10 +5002,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="11" t="n">
         <v>46219</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="11" t="n">
         <v>46249</v>
       </c>
       <c r="N12" s="2" t="n">
@@ -5073,10 +5074,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="11" t="n">
         <v>46225</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="11" t="n">
         <v>46255</v>
       </c>
       <c r="N13" s="2" t="n">
@@ -5145,10 +5146,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="11" t="n">
         <v>46223</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>46253</v>
       </c>
       <c r="N14" s="2" t="n">
@@ -5217,10 +5218,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" s="11" t="n">
         <v>46228</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="11" t="n">
         <v>46258</v>
       </c>
       <c r="N15" s="2" t="n">
@@ -5289,10 +5290,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="11" t="n">
         <v>46232</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="11" t="n">
         <v>46262</v>
       </c>
       <c r="N16" s="2" t="n">
@@ -5361,10 +5362,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="11" t="n">
         <v>46203</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="11" t="n">
         <v>46233</v>
       </c>
       <c r="N17" s="2" t="n">
@@ -5433,10 +5434,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" s="11" t="n">
         <v>46219</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M18" s="11" t="n">
         <v>46249</v>
       </c>
       <c r="N18" s="2" t="n">
@@ -5505,10 +5506,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="11" t="n">
         <v>46225</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="11" t="n">
         <v>46255</v>
       </c>
       <c r="N19" s="2" t="n">
@@ -5581,10 +5582,10 @@
           <t>Trustee meeting &amp; fund accounting support</t>
         </is>
       </c>
-      <c r="L20" s="10" t="n">
+      <c r="L20" s="11" t="n">
         <v>46140</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="11" t="n">
         <v>46170</v>
       </c>
       <c r="N20" s="2" t="n">
@@ -5657,10 +5658,10 @@
           <t>Pension benefit calculation &amp; processing</t>
         </is>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L21" s="11" t="n">
         <v>46170</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="N21" s="2" t="n">
@@ -5733,10 +5734,10 @@
           <t>Fund administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L22" s="11" t="n">
         <v>46190</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>46220</v>
       </c>
       <c r="N22" s="2" t="n">
@@ -5809,10 +5810,10 @@
           <t>COBRA administration &amp; premium billing</t>
         </is>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="11" t="n">
         <v>46186</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="11" t="n">
         <v>46216</v>
       </c>
       <c r="N23" s="2" t="n">
@@ -5881,10 +5882,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="L24" s="11" t="n">
         <v>46200</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="11" t="n">
         <v>46230</v>
       </c>
       <c r="N24" s="2" t="n">
@@ -5953,10 +5954,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L25" s="11" t="n">
         <v>46218</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="11" t="n">
         <v>46248</v>
       </c>
       <c r="N25" s="2" t="n">
@@ -6025,10 +6026,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="L26" s="11" t="n">
         <v>46227</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="11" t="n">
         <v>46257</v>
       </c>
       <c r="N26" s="2" t="n">
@@ -6101,10 +6102,10 @@
           <t>Trustee meeting &amp; fund accounting support</t>
         </is>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="11" t="n">
         <v>46137</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="11" t="n">
         <v>46167</v>
       </c>
       <c r="N27" s="2" t="n">
@@ -6177,10 +6178,10 @@
           <t>Pension benefit calculation &amp; processing</t>
         </is>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" s="11" t="n">
         <v>46166</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="11" t="n">
         <v>46196</v>
       </c>
       <c r="N28" s="2" t="n">
@@ -6253,10 +6254,10 @@
           <t>Fund administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L29" s="10" t="n">
+      <c r="L29" s="11" t="n">
         <v>46193</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="11" t="n">
         <v>46223</v>
       </c>
       <c r="N29" s="2" t="n">
@@ -6325,10 +6326,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="L30" s="11" t="n">
         <v>46199</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="11" t="n">
         <v>46229</v>
       </c>
       <c r="N30" s="2" t="n">
@@ -6397,10 +6398,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="11" t="n">
         <v>46219</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="11" t="n">
         <v>46249</v>
       </c>
       <c r="N31" s="2" t="n">
@@ -6469,10 +6470,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" s="11" t="n">
         <v>46228</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="11" t="n">
         <v>46258</v>
       </c>
       <c r="N32" s="2" t="n">
@@ -6545,10 +6546,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="L33" s="11" t="n">
         <v>46138</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="11" t="n">
         <v>46168</v>
       </c>
       <c r="N33" s="2" t="n">
@@ -6621,10 +6622,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="11" t="n">
         <v>46166</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="11" t="n">
         <v>46196</v>
       </c>
       <c r="N34" s="2" t="n">
@@ -6697,10 +6698,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L35" s="10" t="n">
+      <c r="L35" s="11" t="n">
         <v>46191</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="M35" s="11" t="n">
         <v>46221</v>
       </c>
       <c r="N35" s="2" t="n">
@@ -6773,10 +6774,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="11" t="n">
         <v>46142</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="11" t="n">
         <v>46172</v>
       </c>
       <c r="N36" s="2" t="n">
@@ -6849,10 +6850,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="11" t="n">
         <v>46170</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="N37" s="2" t="n">
@@ -6925,10 +6926,10 @@
           <t>ACA reporting &amp; Form 1095-C services</t>
         </is>
       </c>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="11" t="n">
         <v>46181</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="11" t="n">
         <v>46211</v>
       </c>
       <c r="N38" s="2" t="n">
@@ -7001,10 +7002,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="L39" s="11" t="n">
         <v>46189</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="11" t="n">
         <v>46219</v>
       </c>
       <c r="N39" s="2" t="n">
@@ -7077,10 +7078,10 @@
           <t>ACA reporting &amp; Form 1095-C services</t>
         </is>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="L40" s="11" t="n">
         <v>46008</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="11" t="n">
         <v>46038</v>
       </c>
       <c r="N40" s="2" t="n">
@@ -7153,10 +7154,10 @@
           <t>Collection letter fee - 2nd notice</t>
         </is>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" s="11" t="n">
         <v>46043</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="11" t="n">
         <v>46073</v>
       </c>
       <c r="N41" s="2" t="n">
@@ -7229,10 +7230,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L42" s="10" t="n">
+      <c r="L42" s="11" t="n">
         <v>46087</v>
       </c>
-      <c r="M42" s="10" t="n">
+      <c r="M42" s="11" t="n">
         <v>46117</v>
       </c>
       <c r="N42" s="2" t="n">
@@ -7305,10 +7306,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="11" t="n">
         <v>46127</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="11" t="n">
         <v>46157</v>
       </c>
       <c r="N43" s="2" t="n">
@@ -7381,10 +7382,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L44" s="11" t="n">
         <v>46159</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="11" t="n">
         <v>46189</v>
       </c>
       <c r="N44" s="2" t="n">
@@ -7457,10 +7458,10 @@
           <t>Wage &amp; fringe reconciliation services</t>
         </is>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="11" t="n">
         <v>46025</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="11" t="n">
         <v>46040</v>
       </c>
       <c r="N45" s="2" t="n">
@@ -7533,10 +7534,10 @@
           <t>Collection letter fee - 2nd notice</t>
         </is>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="11" t="n">
         <v>46062</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="11" t="n">
         <v>46077</v>
       </c>
       <c r="N46" s="2" t="n">
@@ -7609,10 +7610,10 @@
           <t>Employer contribution remittance - certified payroll</t>
         </is>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="L47" s="11" t="n">
         <v>46071</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="M47" s="11" t="n">
         <v>46086</v>
       </c>
       <c r="N47" s="2" t="n">
@@ -7685,10 +7686,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="11" t="n">
         <v>46104</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="11" t="n">
         <v>46119</v>
       </c>
       <c r="N48" s="2" t="n">
@@ -7761,10 +7762,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="11" t="n">
         <v>46147</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="11" t="n">
         <v>46162</v>
       </c>
       <c r="N49" s="2" t="n">
@@ -7837,10 +7838,10 @@
           <t>Employer contribution remittance - certified payroll</t>
         </is>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="11" t="n">
         <v>46177</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="11" t="n">
         <v>46192</v>
       </c>
       <c r="N50" s="2" t="n">
@@ -7913,10 +7914,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L51" s="11" t="n">
         <v>46139</v>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="M51" s="11" t="n">
         <v>46169</v>
       </c>
       <c r="N51" s="2" t="n">
@@ -7989,10 +7990,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L52" s="10" t="n">
+      <c r="L52" s="11" t="n">
         <v>46169</v>
       </c>
-      <c r="M52" s="10" t="n">
+      <c r="M52" s="11" t="n">
         <v>46199</v>
       </c>
       <c r="N52" s="2" t="n">
@@ -8065,10 +8066,10 @@
           <t>Employer contribution remittance - certified payroll</t>
         </is>
       </c>
-      <c r="L53" s="10" t="n">
+      <c r="L53" s="11" t="n">
         <v>46192</v>
       </c>
-      <c r="M53" s="10" t="n">
+      <c r="M53" s="11" t="n">
         <v>46222</v>
       </c>
       <c r="N53" s="2" t="n">
@@ -8141,10 +8142,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L54" s="10" t="n">
+      <c r="L54" s="11" t="n">
         <v>46140</v>
       </c>
-      <c r="M54" s="10" t="n">
+      <c r="M54" s="11" t="n">
         <v>46170</v>
       </c>
       <c r="N54" s="2" t="n">
@@ -8217,10 +8218,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L55" s="10" t="n">
+      <c r="L55" s="11" t="n">
         <v>46167</v>
       </c>
-      <c r="M55" s="10" t="n">
+      <c r="M55" s="11" t="n">
         <v>46197</v>
       </c>
       <c r="N55" s="2" t="n">
@@ -8293,10 +8294,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L56" s="10" t="n">
+      <c r="L56" s="11" t="n">
         <v>46188</v>
       </c>
-      <c r="M56" s="10" t="n">
+      <c r="M56" s="11" t="n">
         <v>46218</v>
       </c>
       <c r="N56" s="2" t="n">
@@ -8369,10 +8370,10 @@
           <t>Wage &amp; fringe reconciliation services</t>
         </is>
       </c>
-      <c r="L57" s="10" t="n">
+      <c r="L57" s="11" t="n">
         <v>46009</v>
       </c>
-      <c r="M57" s="10" t="n">
+      <c r="M57" s="11" t="n">
         <v>46039</v>
       </c>
       <c r="N57" s="2" t="n">
@@ -8445,10 +8446,10 @@
           <t>Collection letter fee - 2nd notice</t>
         </is>
       </c>
-      <c r="L58" s="10" t="n">
+      <c r="L58" s="11" t="n">
         <v>46042</v>
       </c>
-      <c r="M58" s="10" t="n">
+      <c r="M58" s="11" t="n">
         <v>46072</v>
       </c>
       <c r="N58" s="2" t="n">
@@ -8521,10 +8522,10 @@
           <t>Employer contribution remittance - certified payroll</t>
         </is>
       </c>
-      <c r="L59" s="10" t="n">
+      <c r="L59" s="11" t="n">
         <v>46052</v>
       </c>
-      <c r="M59" s="10" t="n">
+      <c r="M59" s="11" t="n">
         <v>46082</v>
       </c>
       <c r="N59" s="2" t="n">
@@ -8597,10 +8598,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L60" s="10" t="n">
+      <c r="L60" s="11" t="n">
         <v>46089</v>
       </c>
-      <c r="M60" s="10" t="n">
+      <c r="M60" s="11" t="n">
         <v>46119</v>
       </c>
       <c r="N60" s="2" t="n">
@@ -8673,10 +8674,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L61" s="10" t="n">
+      <c r="L61" s="11" t="n">
         <v>46130</v>
       </c>
-      <c r="M61" s="10" t="n">
+      <c r="M61" s="11" t="n">
         <v>46160</v>
       </c>
       <c r="N61" s="2" t="n">
@@ -8749,10 +8750,10 @@
           <t>Employer contribution remittance - certified payroll</t>
         </is>
       </c>
-      <c r="L62" s="10" t="n">
+      <c r="L62" s="11" t="n">
         <v>46165</v>
       </c>
-      <c r="M62" s="10" t="n">
+      <c r="M62" s="11" t="n">
         <v>46195</v>
       </c>
       <c r="N62" s="2" t="n">
@@ -8825,10 +8826,10 @@
           <t>ACA reporting &amp; Form 1095-C services</t>
         </is>
       </c>
-      <c r="L63" s="10" t="n">
+      <c r="L63" s="11" t="n">
         <v>46028</v>
       </c>
-      <c r="M63" s="10" t="n">
+      <c r="M63" s="11" t="n">
         <v>46043</v>
       </c>
       <c r="N63" s="2" t="n">
@@ -8901,10 +8902,10 @@
           <t>Collection letter fee - 2nd notice</t>
         </is>
       </c>
-      <c r="L64" s="10" t="n">
+      <c r="L64" s="11" t="n">
         <v>46051</v>
       </c>
-      <c r="M64" s="10" t="n">
+      <c r="M64" s="11" t="n">
         <v>46066</v>
       </c>
       <c r="N64" s="2" t="n">
@@ -8977,10 +8978,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L65" s="10" t="n">
+      <c r="L65" s="11" t="n">
         <v>46073</v>
       </c>
-      <c r="M65" s="10" t="n">
+      <c r="M65" s="11" t="n">
         <v>46088</v>
       </c>
       <c r="N65" s="2" t="n">
@@ -9053,10 +9054,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L66" s="10" t="n">
+      <c r="L66" s="11" t="n">
         <v>46104</v>
       </c>
-      <c r="M66" s="10" t="n">
+      <c r="M66" s="11" t="n">
         <v>46119</v>
       </c>
       <c r="N66" s="2" t="n">
@@ -9129,10 +9130,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L67" s="10" t="n">
+      <c r="L67" s="11" t="n">
         <v>46141</v>
       </c>
-      <c r="M67" s="10" t="n">
+      <c r="M67" s="11" t="n">
         <v>46156</v>
       </c>
       <c r="N67" s="2" t="n">
@@ -9205,10 +9206,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L68" s="10" t="n">
+      <c r="L68" s="11" t="n">
         <v>46179</v>
       </c>
-      <c r="M68" s="10" t="n">
+      <c r="M68" s="11" t="n">
         <v>46194</v>
       </c>
       <c r="N68" s="2" t="n">
@@ -9281,10 +9282,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L69" s="10" t="n">
+      <c r="L69" s="11" t="n">
         <v>46139</v>
       </c>
-      <c r="M69" s="10" t="n">
+      <c r="M69" s="11" t="n">
         <v>46169</v>
       </c>
       <c r="N69" s="2" t="n">
@@ -9357,10 +9358,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L70" s="10" t="n">
+      <c r="L70" s="11" t="n">
         <v>46166</v>
       </c>
-      <c r="M70" s="10" t="n">
+      <c r="M70" s="11" t="n">
         <v>46196</v>
       </c>
       <c r="N70" s="2" t="n">
@@ -9433,10 +9434,10 @@
           <t>ACA reporting &amp; Form 1095-C services</t>
         </is>
       </c>
-      <c r="L71" s="10" t="n">
+      <c r="L71" s="11" t="n">
         <v>46182</v>
       </c>
-      <c r="M71" s="10" t="n">
+      <c r="M71" s="11" t="n">
         <v>46212</v>
       </c>
       <c r="N71" s="2" t="n">
@@ -9509,10 +9510,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L72" s="10" t="n">
+      <c r="L72" s="11" t="n">
         <v>46188</v>
       </c>
-      <c r="M72" s="10" t="n">
+      <c r="M72" s="11" t="n">
         <v>46218</v>
       </c>
       <c r="N72" s="2" t="n">
@@ -9581,10 +9582,10 @@
           <t>Delinquency assessment &amp; liquidated damages</t>
         </is>
       </c>
-      <c r="L73" s="10" t="n">
+      <c r="L73" s="11" t="n">
         <v>46203</v>
       </c>
-      <c r="M73" s="10" t="n">
+      <c r="M73" s="11" t="n">
         <v>46233</v>
       </c>
       <c r="N73" s="2" t="n">
@@ -9653,10 +9654,10 @@
           <t>Employer contribution remittance - monthly</t>
         </is>
       </c>
-      <c r="L74" s="10" t="n">
+      <c r="L74" s="11" t="n">
         <v>46217</v>
       </c>
-      <c r="M74" s="10" t="n">
+      <c r="M74" s="11" t="n">
         <v>46247</v>
       </c>
       <c r="N74" s="2" t="n">
@@ -9725,10 +9726,10 @@
           <t>Payroll compliance audit recovery</t>
         </is>
       </c>
-      <c r="L75" s="10" t="n">
+      <c r="L75" s="11" t="n">
         <v>46224</v>
       </c>
-      <c r="M75" s="10" t="n">
+      <c r="M75" s="11" t="n">
         <v>46254</v>
       </c>
       <c r="N75" s="2" t="n">
@@ -9797,10 +9798,10 @@
           <t>Retiree &amp; OPEB benefit administration</t>
         </is>
       </c>
-      <c r="L76" s="10" t="n">
+      <c r="L76" s="11" t="n">
         <v>46188</v>
       </c>
-      <c r="M76" s="10" t="n">
+      <c r="M76" s="11" t="n">
         <v>46233</v>
       </c>
       <c r="N76" s="2" t="n">
@@ -9869,10 +9870,10 @@
           <t>Plan administration fee - per employee per month</t>
         </is>
       </c>
-      <c r="L77" s="10" t="n">
+      <c r="L77" s="11" t="n">
         <v>46200</v>
       </c>
-      <c r="M77" s="10" t="n">
+      <c r="M77" s="11" t="n">
         <v>46245</v>
       </c>
       <c r="N77" s="2" t="n">
@@ -9941,10 +9942,10 @@
           <t>Open enrollment services &amp; member communications</t>
         </is>
       </c>
-      <c r="L78" s="10" t="n">
+      <c r="L78" s="11" t="n">
         <v>46213</v>
       </c>
-      <c r="M78" s="10" t="n">
+      <c r="M78" s="11" t="n">
         <v>46258</v>
       </c>
       <c r="N78" s="2" t="n">
@@ -10013,10 +10014,10 @@
           <t>Retiree &amp; OPEB benefit administration</t>
         </is>
       </c>
-      <c r="L79" s="10" t="n">
+      <c r="L79" s="11" t="n">
         <v>46205</v>
       </c>
-      <c r="M79" s="10" t="n">
+      <c r="M79" s="11" t="n">
         <v>46250</v>
       </c>
       <c r="N79" s="2" t="n">
@@ -10085,10 +10086,10 @@
           <t>Open enrollment services &amp; member communications</t>
         </is>
       </c>
-      <c r="L80" s="10" t="n">
+      <c r="L80" s="11" t="n">
         <v>46213</v>
       </c>
-      <c r="M80" s="10" t="n">
+      <c r="M80" s="11" t="n">
         <v>46258</v>
       </c>
       <c r="N80" s="2" t="n">
@@ -10157,10 +10158,10 @@
           <t>Plan administration fee - per employee per month</t>
         </is>
       </c>
-      <c r="L81" s="10" t="n">
+      <c r="L81" s="11" t="n">
         <v>46217</v>
       </c>
-      <c r="M81" s="10" t="n">
+      <c r="M81" s="11" t="n">
         <v>46262</v>
       </c>
       <c r="N81" s="2" t="n">
@@ -10229,10 +10230,10 @@
           <t>Retiree &amp; OPEB benefit administration</t>
         </is>
       </c>
-      <c r="L82" s="10" t="n">
+      <c r="L82" s="11" t="n">
         <v>46186</v>
       </c>
-      <c r="M82" s="10" t="n">
+      <c r="M82" s="11" t="n">
         <v>46231</v>
       </c>
       <c r="N82" s="2" t="n">
@@ -10301,10 +10302,10 @@
           <t>Plan administration fee - per employee per month</t>
         </is>
       </c>
-      <c r="L83" s="10" t="n">
+      <c r="L83" s="11" t="n">
         <v>46198</v>
       </c>
-      <c r="M83" s="10" t="n">
+      <c r="M83" s="11" t="n">
         <v>46243</v>
       </c>
       <c r="N83" s="2" t="n">
@@ -10373,10 +10374,10 @@
           <t>Open enrollment services &amp; member communications</t>
         </is>
       </c>
-      <c r="L84" s="10" t="n">
+      <c r="L84" s="11" t="n">
         <v>46209</v>
       </c>
-      <c r="M84" s="10" t="n">
+      <c r="M84" s="11" t="n">
         <v>46254</v>
       </c>
       <c r="N84" s="2" t="n">
@@ -10445,10 +10446,10 @@
           <t>Retiree &amp; OPEB benefit administration</t>
         </is>
       </c>
-      <c r="L85" s="10" t="n">
+      <c r="L85" s="11" t="n">
         <v>46171</v>
       </c>
-      <c r="M85" s="10" t="n">
+      <c r="M85" s="11" t="n">
         <v>46231</v>
       </c>
       <c r="N85" s="2" t="n">
@@ -10517,10 +10518,10 @@
           <t>Plan administration fee - per employee per month</t>
         </is>
       </c>
-      <c r="L86" s="10" t="n">
+      <c r="L86" s="11" t="n">
         <v>46186</v>
       </c>
-      <c r="M86" s="10" t="n">
+      <c r="M86" s="11" t="n">
         <v>46246</v>
       </c>
       <c r="N86" s="2" t="n">
@@ -10589,10 +10590,10 @@
           <t>Open enrollment services &amp; member communications</t>
         </is>
       </c>
-      <c r="L87" s="10" t="n">
+      <c r="L87" s="11" t="n">
         <v>46194</v>
       </c>
-      <c r="M87" s="10" t="n">
+      <c r="M87" s="11" t="n">
         <v>46254</v>
       </c>
       <c r="N87" s="2" t="n">
@@ -10661,10 +10662,10 @@
           <t>Retiree &amp; OPEB benefit administration</t>
         </is>
       </c>
-      <c r="L88" s="10" t="n">
+      <c r="L88" s="11" t="n">
         <v>46186</v>
       </c>
-      <c r="M88" s="10" t="n">
+      <c r="M88" s="11" t="n">
         <v>46231</v>
       </c>
       <c r="N88" s="2" t="n">
@@ -10733,10 +10734,10 @@
           <t>Plan administration fee - per employee per month</t>
         </is>
       </c>
-      <c r="L89" s="10" t="n">
+      <c r="L89" s="11" t="n">
         <v>46204</v>
       </c>
-      <c r="M89" s="10" t="n">
+      <c r="M89" s="11" t="n">
         <v>46249</v>
       </c>
       <c r="N89" s="2" t="n">
@@ -10805,10 +10806,10 @@
           <t>Open enrollment services &amp; member communications</t>
         </is>
       </c>
-      <c r="L90" s="10" t="n">
+      <c r="L90" s="11" t="n">
         <v>46209</v>
       </c>
-      <c r="M90" s="10" t="n">
+      <c r="M90" s="11" t="n">
         <v>46254</v>
       </c>
       <c r="N90" s="2" t="n">
@@ -10877,10 +10878,10 @@
           <t>COBRA administration &amp; premium billing</t>
         </is>
       </c>
-      <c r="L91" s="10" t="n">
+      <c r="L91" s="11" t="n">
         <v>46187</v>
       </c>
-      <c r="M91" s="10" t="n">
+      <c r="M91" s="11" t="n">
         <v>46217</v>
       </c>
       <c r="N91" s="2" t="n">
@@ -10949,10 +10950,10 @@
           <t>Claims processing &amp; adjudication services</t>
         </is>
       </c>
-      <c r="L92" s="10" t="n">
+      <c r="L92" s="11" t="n">
         <v>46204</v>
       </c>
-      <c r="M92" s="10" t="n">
+      <c r="M92" s="11" t="n">
         <v>46234</v>
       </c>
       <c r="N92" s="2" t="n">
@@ -11021,10 +11022,10 @@
           <t>Administration fee - per participant per month</t>
         </is>
       </c>
-      <c r="L93" s="10" t="n">
+      <c r="L93" s="11" t="n">
         <v>46218</v>
       </c>
-      <c r="M93" s="10" t="n">
+      <c r="M93" s="11" t="n">
         <v>46248</v>
       </c>
       <c r="N93" s="2" t="n">
@@ -11093,10 +11094,10 @@
           <t>Eligibility &amp; enrollment administration</t>
         </is>
       </c>
-      <c r="L94" s="10" t="n">
+      <c r="L94" s="11" t="n">
         <v>46223</v>
       </c>
-      <c r="M94" s="10" t="n">
+      <c r="M94" s="11" t="n">
         <v>46253</v>
       </c>
       <c r="N94" s="2" t="n">
@@ -11266,7 +11267,7 @@
       <c r="G2" s="8" t="n">
         <v>89709.95</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="11" t="n">
         <v>46204</v>
       </c>
       <c r="I2" s="8" t="n">
@@ -11323,7 +11324,7 @@
       <c r="G3" s="8" t="n">
         <v>49322.51</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" s="11" t="n">
         <v>46211</v>
       </c>
       <c r="I3" s="8" t="n">
@@ -11380,7 +11381,7 @@
       <c r="G4" s="8" t="n">
         <v>41911.42</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="11" t="n">
         <v>46198</v>
       </c>
       <c r="I4" s="8" t="n">
@@ -11437,7 +11438,7 @@
       <c r="G5" s="8" t="n">
         <v>111035.16</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="11" t="n">
         <v>46194</v>
       </c>
       <c r="I5" s="8" t="n">
@@ -11494,7 +11495,7 @@
       <c r="G6" s="8" t="n">
         <v>58816.94</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="11" t="n">
         <v>46202</v>
       </c>
       <c r="I6" s="8" t="n">
@@ -11551,7 +11552,7 @@
       <c r="G7" s="8" t="n">
         <v>58610.41</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="11" t="n">
         <v>46200</v>
       </c>
       <c r="I7" s="8" t="n">
@@ -11608,7 +11609,7 @@
       <c r="G8" s="8" t="n">
         <v>87988.02</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="11" t="n">
         <v>46188</v>
       </c>
       <c r="I8" s="8" t="n">
@@ -11665,7 +11666,7 @@
       <c r="G9" s="8" t="n">
         <v>123838.26</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="11" t="n">
         <v>46197</v>
       </c>
       <c r="I9" s="8" t="n">
@@ -11722,7 +11723,7 @@
       <c r="G10" s="8" t="n">
         <v>58294.27</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="11" t="n">
         <v>46181</v>
       </c>
       <c r="I10" s="8" t="n">
@@ -11779,7 +11780,7 @@
       <c r="G11" s="8" t="n">
         <v>71545.52</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="11" t="n">
         <v>46193</v>
       </c>
       <c r="I11" s="8" t="n">
@@ -11836,7 +11837,7 @@
       <c r="G12" s="8" t="n">
         <v>39485.64</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="11" t="n">
         <v>46176</v>
       </c>
       <c r="I12" s="8" t="n">
@@ -11893,7 +11894,7 @@
       <c r="G13" s="8" t="n">
         <v>54077.31</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="11" t="n">
         <v>46148</v>
       </c>
       <c r="I13" s="8" t="n">
@@ -11950,7 +11951,7 @@
       <c r="G14" s="8" t="n">
         <v>76376.42</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="H14" s="11" t="n">
         <v>46147</v>
       </c>
       <c r="I14" s="8" t="n">
@@ -12007,7 +12008,7 @@
       <c r="G15" s="8" t="n">
         <v>92708.10000000001</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="11" t="n">
         <v>46125</v>
       </c>
       <c r="I15" s="8" t="n">
@@ -12064,7 +12065,7 @@
       <c r="G16" s="8" t="n">
         <v>109471.98</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="11" t="n">
         <v>46153</v>
       </c>
       <c r="I16" s="8" t="n">
@@ -12121,7 +12122,7 @@
       <c r="G17" s="8" t="n">
         <v>55808.94</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="H17" s="11" t="n">
         <v>46164</v>
       </c>
       <c r="I17" s="8" t="n">
@@ -12178,7 +12179,7 @@
       <c r="G18" s="8" t="n">
         <v>59329.73</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="H18" s="11" t="n">
         <v>46107</v>
       </c>
       <c r="I18" s="8" t="n">
@@ -12235,7 +12236,7 @@
       <c r="G19" s="8" t="n">
         <v>138400.03</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" s="11" t="n">
         <v>46115</v>
       </c>
       <c r="I19" s="8" t="n">
@@ -12292,7 +12293,7 @@
       <c r="G20" s="8" t="n">
         <v>29829.81</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H20" s="11" t="n">
         <v>46137</v>
       </c>
       <c r="I20" s="8" t="n">
@@ -12349,7 +12350,7 @@
       <c r="G21" s="8" t="n">
         <v>51704.06</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" s="11" t="n">
         <v>46167</v>
       </c>
       <c r="I21" s="8" t="n">
@@ -12406,7 +12407,7 @@
       <c r="G22" s="8" t="n">
         <v>54729.16</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="H22" s="11" t="n">
         <v>46196</v>
       </c>
       <c r="I22" s="8" t="n">
@@ -12463,7 +12464,7 @@
       <c r="G23" s="8" t="n">
         <v>71329.02</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="H23" s="11" t="n">
         <v>46204</v>
       </c>
       <c r="I23" s="8" t="n">
@@ -12520,7 +12521,7 @@
       <c r="G24" s="8" t="n">
         <v>32172.8</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="H24" s="11" t="n">
         <v>46193</v>
       </c>
       <c r="I24" s="8" t="n">
@@ -12577,7 +12578,7 @@
       <c r="G25" s="8" t="n">
         <v>76609.46000000001</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="11" t="n">
         <v>46193</v>
       </c>
       <c r="I25" s="8" t="n">
@@ -12634,7 +12635,7 @@
       <c r="G26" s="8" t="n">
         <v>90949.36</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H26" s="11" t="n">
         <v>46187</v>
       </c>
       <c r="I26" s="8" t="n">
@@ -12691,7 +12692,7 @@
       <c r="G27" s="8" t="n">
         <v>29840.47</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H27" s="11" t="n">
         <v>46183</v>
       </c>
       <c r="I27" s="8" t="n">
@@ -12817,7 +12818,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E2" s="8" t="n">
@@ -12855,7 +12856,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E3" s="8" t="n">
@@ -12893,7 +12894,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E4" s="8" t="n">
@@ -12931,7 +12932,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E5" s="8" t="n">
@@ -12969,7 +12970,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -13007,7 +13008,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E7" s="8" t="n">
@@ -13045,7 +13046,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -13083,7 +13084,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E9" s="8" t="n">
@@ -13121,7 +13122,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -13159,7 +13160,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -13197,7 +13198,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -13235,7 +13236,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -13273,7 +13274,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -13311,7 +13312,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E15" s="8" t="n">
@@ -13349,7 +13350,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -13387,7 +13388,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E17" s="8" t="n">
@@ -13425,7 +13426,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -13463,7 +13464,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E19" s="8" t="n">
@@ -13501,7 +13502,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -13539,7 +13540,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E21" s="8" t="n">
@@ -13577,7 +13578,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -13615,7 +13616,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E23" s="8" t="n">
@@ -13653,7 +13654,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -13691,7 +13692,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E25" s="8" t="n">
@@ -13729,7 +13730,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -13767,7 +13768,7 @@
           <t>30_60_90_180</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="E27" s="8" t="n">
